--- a/Datasheets/pcbuilder_import_data_20260904_cpus.xlsx
+++ b/Datasheets/pcbuilder_import_data_20260904_cpus.xlsx
@@ -445,7 +445,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,7 +457,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -515,14 +515,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -532,14 +532,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4f5ee58c-3042-41bb-994e-263c6db6b98c</t>
+          <t>89f39647-02c6-4e3a-a7e2-11537ac4b025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,14 +549,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ac96b363-c436-4bfc-b0ea-bb5ad66fb03e</t>
+          <t>906cdde8-5cc2-4022-ac34-8cbc677e4872</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>c5dbc0b7-e524-4709-b69f-1820cc70658b</t>
+          <t>a9b5a988-eed6-4636-834b-890dc0b34753</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -642,19 +642,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ac96b363-c436-4bfc-b0ea-bb5ad66fb03e</t>
+          <t>906cdde8-5cc2-4022-ac34-8cbc677e4872</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>368340ba-e89e-4432-b7d9-41020df53695</t>
+          <t>eb1c7c30-7535-48d6-8794-decc126ce213</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -664,19 +664,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00bbc147-f2df-443b-91e1-111ea7b0768e</t>
+          <t>340a2b28-3d18-4f30-8139-d4545e177e29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -686,19 +686,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8d916192-8262-48da-b577-69ce6d8c2dca</t>
+          <t>12ab2f89-711e-43cd-b1b3-d94ae7518c8e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -708,19 +708,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>421fca16-16f0-4ebd-ac68-6e279204fbed</t>
+          <t>e34aefe4-065f-45f8-b878-be2b12f8a486</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>68e6e02f-a764-4dc0-8451-c02a64951633</t>
+          <t>dc635b21-c3dc-402b-a109-be3305b8305f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -752,19 +752,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>90f4da28-170d-4217-ab7a-bee9179a32b4</t>
+          <t>e460487a-ac29-40d2-8b28-e50b8e0ebac4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -774,19 +774,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>b4005579-9fb3-433a-8fac-defcec689a48</t>
+          <t>31f95f32-d7e9-4395-9694-17270a8ce5e7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -796,19 +796,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dd8ada77-2f53-4b5d-a586-5cf73fa91c23</t>
+          <t>729bd713-1bc3-45b0-9a02-7b97d1fe0aa5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -818,19 +818,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3b47a228-1a5e-45ec-bf7b-b67b65da611f</t>
+          <t>b8bb88d0-6910-4320-a20b-2e9a2d4dab2f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4f5ee58c-3042-41bb-994e-263c6db6b98c</t>
+          <t>89f39647-02c6-4e3a-a7e2-11537ac4b025</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bad3a566-5d6e-4d87-81bd-fced79f8e175</t>
+          <t>99bec8e0-b1d1-480e-aad6-2bec3b817abc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ac96b363-c436-4bfc-b0ea-bb5ad66fb03e</t>
+          <t>906cdde8-5cc2-4022-ac34-8cbc677e4872</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -916,7 +916,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2f4dded7-ca07-4cbb-bec6-91c58623eeac</t>
+          <t>031b4e12-e71d-4809-a3ae-c2d92e7a8bfe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ac96b363-c436-4bfc-b0ea-bb5ad66fb03e</t>
+          <t>906cdde8-5cc2-4022-ac34-8cbc677e4872</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -938,7 +938,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>36957076-d929-4a0e-9477-cde2b8252113</t>
+          <t>2c39feb0-fbd6-4e85-bfc9-8d74c63fdb91</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ac96b363-c436-4bfc-b0ea-bb5ad66fb03e</t>
+          <t>906cdde8-5cc2-4022-ac34-8cbc677e4872</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -960,7 +960,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1070,7 +1070,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1092,7 +1092,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1114,7 +1114,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1136,7 +1136,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1158,7 +1158,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>c80e226c-e7aa-4c80-a79e-ebe0ed500fbe</t>
+          <t>2d004edf-399c-4fbd-8582-8cfd81acacbf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1180,7 +1180,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7833e174-abc5-49b4-be76-b2e3be854d7b</t>
+          <t>46e9bcd9-0de3-41da-a8c5-01509c0c0487</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>60b9643b-0881-49d1-ac41-c033fda5c483</t>
+          <t>76f34cd0-e89e-43df-b949-23b206ace7fd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1224,7 +1224,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>61fe1e3d-8de8-4637-bd7a-023a3bc04a56</t>
+          <t>ace42842-28e0-4447-9be9-043baa73d86f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4daab51d-06a3-4f0d-9aa0-eb4cfa19681f</t>
+          <t>be27f6c8-2c6d-4d9e-948a-e57857a0f547</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1268,7 +1268,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3b1fe548-1449-4d56-9830-30e42cd3962f</t>
+          <t>184e02f2-0f5a-495e-81cd-880a42a6b609</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2e269c7a-bc77-4068-a8c6-09caa1e70b3e</t>
+          <t>5348db8d-77c0-4d9d-819d-ccd61738ff91</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1312,7 +1312,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922ea59a-282b-45f8-87c6-25c231d19b8c</t>
+          <t>74c46482-bce7-4624-b428-58bb6a007373</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>67719a3c-97b5-419a-93d1-ac67d2790ea8</t>
+          <t>9ac8b8c7-9059-4f90-9eee-12b427f45b35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1356,7 +1356,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>b4a1d8d5-8755-4f0c-be0d-31f66fd24dd5</t>
+          <t>6081bf84-191d-442a-87ec-7fde1cead1f5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>b7791b79-930d-464d-9166-7097ffd6c45e</t>
+          <t>6baae17d-3770-4861-b4f1-ed5a1470b88e</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1400,7 +1400,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>78ad8a66-6674-4926-8c4e-ad4249d6a229</t>
+          <t>20ea0e39-7505-4245-881d-c736b3ced2b9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1422,7 +1422,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>30142cdf-fcc1-45d0-92da-93b8221253c2</t>
+          <t>a691f620-f8fc-4657-806d-f0a40e669523</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>db5d1efd-0263-43fb-9037-59d0abb93ef0</t>
+          <t>7c08996c-42a3-4903-9616-e29043f859bb</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>57c00b85-dcec-4183-b966-5be4960d354b</t>
+          <t>8d3f77ee-4bdb-4b8c-8ebc-80cb0b9a17fa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1488,7 +1488,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8894872e-c260-4607-86bc-ef3ac32354ab</t>
+          <t>ada0d8e1-7143-4db4-a835-f33f8bd0d93e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4f5ee58c-3042-41bb-994e-263c6db6b98c</t>
+          <t>89f39647-02c6-4e3a-a7e2-11537ac4b025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1510,7 +1510,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29820b40-02d7-4a16-bbac-94c94d207517</t>
+          <t>77ef5ee1-2752-4cad-8a84-94fe6e69de2d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4f5ee58c-3042-41bb-994e-263c6db6b98c</t>
+          <t>89f39647-02c6-4e3a-a7e2-11537ac4b025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1532,7 +1532,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>099eef3b-9c13-4399-948b-e7270b2743d7</t>
+          <t>888c29c4-2c39-45d0-b508-825412755dae</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4f5ee58c-3042-41bb-994e-263c6db6b98c</t>
+          <t>89f39647-02c6-4e3a-a7e2-11537ac4b025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ac96b363-c436-4bfc-b0ea-bb5ad66fb03e</t>
+          <t>906cdde8-5cc2-4022-ac34-8cbc677e4872</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>c5dbc0b7-e524-4709-b69f-1820cc70658b</t>
+          <t>a9b5a988-eed6-4636-834b-890dc0b34753</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1668,17 +1668,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ac96b363-c436-4bfc-b0ea-bb5ad66fb03e</t>
+          <t>906cdde8-5cc2-4022-ac34-8cbc677e4872</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>c5dbc0b7-e524-4709-b69f-1820cc70658b</t>
+          <t>a9b5a988-eed6-4636-834b-890dc0b34753</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ac96b363-c436-4bfc-b0ea-bb5ad66fb03e</t>
+          <t>906cdde8-5cc2-4022-ac34-8cbc677e4872</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>c5dbc0b7-e524-4709-b69f-1820cc70658b</t>
+          <t>a9b5a988-eed6-4636-834b-890dc0b34753</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ac96b363-c436-4bfc-b0ea-bb5ad66fb03e</t>
+          <t>906cdde8-5cc2-4022-ac34-8cbc677e4872</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>c5dbc0b7-e524-4709-b69f-1820cc70658b</t>
+          <t>a9b5a988-eed6-4636-834b-890dc0b34753</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ac96b363-c436-4bfc-b0ea-bb5ad66fb03e</t>
+          <t>906cdde8-5cc2-4022-ac34-8cbc677e4872</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>c5dbc0b7-e524-4709-b69f-1820cc70658b</t>
+          <t>a9b5a988-eed6-4636-834b-890dc0b34753</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>368340ba-e89e-4432-b7d9-41020df53695</t>
+          <t>eb1c7c30-7535-48d6-8794-decc126ce213</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>368340ba-e89e-4432-b7d9-41020df53695</t>
+          <t>eb1c7c30-7535-48d6-8794-decc126ce213</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>368340ba-e89e-4432-b7d9-41020df53695</t>
+          <t>eb1c7c30-7535-48d6-8794-decc126ce213</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1927,17 +1927,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>368340ba-e89e-4432-b7d9-41020df53695</t>
+          <t>eb1c7c30-7535-48d6-8794-decc126ce213</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>368340ba-e89e-4432-b7d9-41020df53695</t>
+          <t>eb1c7c30-7535-48d6-8794-decc126ce213</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00bbc147-f2df-443b-91e1-111ea7b0768e</t>
+          <t>340a2b28-3d18-4f30-8139-d4545e177e29</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00bbc147-f2df-443b-91e1-111ea7b0768e</t>
+          <t>340a2b28-3d18-4f30-8139-d4545e177e29</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8d916192-8262-48da-b577-69ce6d8c2dca</t>
+          <t>12ab2f89-711e-43cd-b1b3-d94ae7518c8e</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8d916192-8262-48da-b577-69ce6d8c2dca</t>
+          <t>12ab2f89-711e-43cd-b1b3-d94ae7518c8e</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8d916192-8262-48da-b577-69ce6d8c2dca</t>
+          <t>12ab2f89-711e-43cd-b1b3-d94ae7518c8e</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2186,17 +2186,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>a85691f1-ec3a-4b58-8052-f0c22980286a</t>
+          <t>04bd0d18-b83d-4e30-a5d2-c052ab3c84ca</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>52df6ddf-e19d-4b6b-ae6b-81cc439ea541</t>
+          <t>2ff24ca3-bc12-421e-9912-0e44bd2748c7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8d916192-8262-48da-b577-69ce6d8c2dca</t>
+          <t>12ab2f89-711e-43cd-b1b3-d94ae7518c8e</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2223,17 +2223,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>421fca16-16f0-4ebd-ac68-6e279204fbed</t>
+          <t>e34aefe4-065f-45f8-b878-be2b12f8a486</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>421fca16-16f0-4ebd-ac68-6e279204fbed</t>
+          <t>e34aefe4-065f-45f8-b878-be2b12f8a486</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>421fca16-16f0-4ebd-ac68-6e279204fbed</t>
+          <t>e34aefe4-065f-45f8-b878-be2b12f8a486</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>68e6e02f-a764-4dc0-8451-c02a64951633</t>
+          <t>dc635b21-c3dc-402b-a109-be3305b8305f</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>68e6e02f-a764-4dc0-8451-c02a64951633</t>
+          <t>dc635b21-c3dc-402b-a109-be3305b8305f</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2408,17 +2408,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17831430-348c-4e2c-a634-a61fd0ba88b7</t>
+          <t>320f15bb-4f9f-4727-9a17-028865d1ac1c</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>68e6e02f-a764-4dc0-8451-c02a64951633</t>
+          <t>dc635b21-c3dc-402b-a109-be3305b8305f</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2445,17 +2445,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>90f4da28-170d-4217-ab7a-bee9179a32b4</t>
+          <t>e460487a-ac29-40d2-8b28-e50b8e0ebac4</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>90f4da28-170d-4217-ab7a-bee9179a32b4</t>
+          <t>e460487a-ac29-40d2-8b28-e50b8e0ebac4</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>90f4da28-170d-4217-ab7a-bee9179a32b4</t>
+          <t>e460487a-ac29-40d2-8b28-e50b8e0ebac4</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>b4005579-9fb3-433a-8fac-defcec689a48</t>
+          <t>31f95f32-d7e9-4395-9694-17270a8ce5e7</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2593,17 +2593,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>b4005579-9fb3-433a-8fac-defcec689a48</t>
+          <t>31f95f32-d7e9-4395-9694-17270a8ce5e7</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2630,17 +2630,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>b4005579-9fb3-433a-8fac-defcec689a48</t>
+          <t>31f95f32-d7e9-4395-9694-17270a8ce5e7</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>b4005579-9fb3-433a-8fac-defcec689a48</t>
+          <t>31f95f32-d7e9-4395-9694-17270a8ce5e7</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>dd8ada77-2f53-4b5d-a586-5cf73fa91c23</t>
+          <t>729bd713-1bc3-45b0-9a02-7b97d1fe0aa5</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>dd8ada77-2f53-4b5d-a586-5cf73fa91c23</t>
+          <t>729bd713-1bc3-45b0-9a02-7b97d1fe0aa5</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2778,17 +2778,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>47de4e3b-9040-4f73-9b2e-f071a7e69386</t>
+          <t>a2c9596d-60f1-4ee9-a3d0-063cb9249d23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>dd8ada77-2f53-4b5d-a586-5cf73fa91c23</t>
+          <t>729bd713-1bc3-45b0-9a02-7b97d1fe0aa5</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2815,17 +2815,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4f5ee58c-3042-41bb-994e-263c6db6b98c</t>
+          <t>89f39647-02c6-4e3a-a7e2-11537ac4b025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3b47a228-1a5e-45ec-bf7b-b67b65da611f</t>
+          <t>b8bb88d0-6910-4320-a20b-2e9a2d4dab2f</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4f5ee58c-3042-41bb-994e-263c6db6b98c</t>
+          <t>89f39647-02c6-4e3a-a7e2-11537ac4b025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3b47a228-1a5e-45ec-bf7b-b67b65da611f</t>
+          <t>b8bb88d0-6910-4320-a20b-2e9a2d4dab2f</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2889,17 +2889,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>d4ca1382-75eb-46e4-b84b-a498e01d11b3</t>
+          <t>4e3bea87-6932-4819-8db2-85728f581277</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4f5ee58c-3042-41bb-994e-263c6db6b98c</t>
+          <t>89f39647-02c6-4e3a-a7e2-11537ac4b025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3b47a228-1a5e-45ec-bf7b-b67b65da611f</t>
+          <t>b8bb88d0-6910-4320-a20b-2e9a2d4dab2f</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bad3a566-5d6e-4d87-81bd-fced79f8e175</t>
+          <t>99bec8e0-b1d1-480e-aad6-2bec3b817abc</t>
         </is>
       </c>
       <c r="C2" t="b">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2f4dded7-ca07-4cbb-bec6-91c58623eeac</t>
+          <t>031b4e12-e71d-4809-a3ae-c2d92e7a8bfe</t>
         </is>
       </c>
       <c r="C3" t="b">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36957076-d929-4a0e-9477-cde2b8252113</t>
+          <t>2c39feb0-fbd6-4e85-bfc9-8d74c63fdb91</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bad3a566-5d6e-4d87-81bd-fced79f8e175</t>
+          <t>99bec8e0-b1d1-480e-aad6-2bec3b817abc</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2f4dded7-ca07-4cbb-bec6-91c58623eeac</t>
+          <t>031b4e12-e71d-4809-a3ae-c2d92e7a8bfe</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36957076-d929-4a0e-9477-cde2b8252113</t>
+          <t>2c39feb0-fbd6-4e85-bfc9-8d74c63fdb91</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bad3a566-5d6e-4d87-81bd-fced79f8e175</t>
+          <t>99bec8e0-b1d1-480e-aad6-2bec3b817abc</t>
         </is>
       </c>
       <c r="C8" t="b">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2f4dded7-ca07-4cbb-bec6-91c58623eeac</t>
+          <t>031b4e12-e71d-4809-a3ae-c2d92e7a8bfe</t>
         </is>
       </c>
       <c r="C9" t="b">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>36957076-d929-4a0e-9477-cde2b8252113</t>
+          <t>2c39feb0-fbd6-4e85-bfc9-8d74c63fdb91</t>
         </is>
       </c>
       <c r="C10" t="b">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bad3a566-5d6e-4d87-81bd-fced79f8e175</t>
+          <t>99bec8e0-b1d1-480e-aad6-2bec3b817abc</t>
         </is>
       </c>
       <c r="C11" t="b">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2f4dded7-ca07-4cbb-bec6-91c58623eeac</t>
+          <t>031b4e12-e71d-4809-a3ae-c2d92e7a8bfe</t>
         </is>
       </c>
       <c r="C12" t="b">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36957076-d929-4a0e-9477-cde2b8252113</t>
+          <t>2c39feb0-fbd6-4e85-bfc9-8d74c63fdb91</t>
         </is>
       </c>
       <c r="C13" t="b">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bad3a566-5d6e-4d87-81bd-fced79f8e175</t>
+          <t>99bec8e0-b1d1-480e-aad6-2bec3b817abc</t>
         </is>
       </c>
       <c r="C14" t="b">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2f4dded7-ca07-4cbb-bec6-91c58623eeac</t>
+          <t>031b4e12-e71d-4809-a3ae-c2d92e7a8bfe</t>
         </is>
       </c>
       <c r="C15" t="b">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>36957076-d929-4a0e-9477-cde2b8252113</t>
+          <t>2c39feb0-fbd6-4e85-bfc9-8d74c63fdb91</t>
         </is>
       </c>
       <c r="C16" t="b">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="C17" t="b">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="C18" t="b">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="C19" t="b">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="C20" t="b">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="C21" t="b">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="C22" t="b">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="C23" t="b">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="C24" t="b">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="C25" t="b">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="C26" t="b">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="C27" t="b">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="C28" t="b">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="C29" t="b">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="C30" t="b">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="C31" t="b">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="C32" t="b">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="C33" t="b">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="C34" t="b">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="C35" t="b">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="C36" t="b">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="C37" t="b">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="C38" t="b">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="C39" t="b">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="C40" t="b">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="C41" t="b">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="C42" t="b">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="C43" t="b">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="C44" t="b">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="C45" t="b">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="C46" t="b">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="C47" t="b">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="C48" t="b">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="C49" t="b">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="C50" t="b">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="C51" t="b">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="C52" t="b">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="C53" t="b">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="C54" t="b">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="C55" t="b">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="C56" t="b">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="C57" t="b">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="C58" t="b">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="C59" t="b">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="C60" t="b">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="C61" t="b">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="C62" t="b">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="C63" t="b">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="C64" t="b">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="C65" t="b">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="C66" t="b">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="C67" t="b">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="C68" t="b">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="C69" t="b">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="C70" t="b">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="C71" t="b">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="C72" t="b">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="C73" t="b">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="C74" t="b">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="C75" t="b">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="C76" t="b">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="C77" t="b">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="C78" t="b">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="C79" t="b">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="C80" t="b">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="C81" t="b">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="C82" t="b">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="C83" t="b">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="C84" t="b">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="C85" t="b">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="C86" t="b">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="C87" t="b">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="C88" t="b">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="C89" t="b">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="C90" t="b">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="C91" t="b">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="C92" t="b">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="C93" t="b">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="C94" t="b">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="C95" t="b">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="C96" t="b">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="C97" t="b">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="C98" t="b">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="C99" t="b">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="C100" t="b">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="C101" t="b">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="C102" t="b">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="C103" t="b">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="C104" t="b">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="C105" t="b">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="C106" t="b">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>d8aebfdc-6784-462e-bdd0-c8c51856197e</t>
+          <t>962c5072-3646-412d-a05e-01e50473a823</t>
         </is>
       </c>
       <c r="C107" t="b">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>77eac08b-f78e-4ab5-9abf-9819fb8b6737</t>
+          <t>724a6344-cbb4-46f2-af5f-d128f92c73b9</t>
         </is>
       </c>
       <c r="C108" t="b">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>e46e9e4b-0f58-4af6-8194-7347e3c30910</t>
+          <t>667f0e1e-446b-4d90-bbf5-3269902586bf</t>
         </is>
       </c>
       <c r="C109" t="b">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>8442bed6-c12b-4108-a31b-37c8fb8eb422</t>
+          <t>3f8b09ea-6671-409c-8d74-a145b05a5123</t>
         </is>
       </c>
       <c r="C110" t="b">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>e462c731-7027-49d2-9999-e22fdbeae188</t>
+          <t>4d364e48-cfba-4741-a22f-00e6f6f4e2bb</t>
         </is>
       </c>
       <c r="C111" t="b">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>d8becfe5-0dfe-465a-af5d-48a9d54e8042</t>
+          <t>0d61752d-aa7d-4481-a255-4a745d1a0c8d</t>
         </is>
       </c>
       <c r="C112" t="b">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>560c4a4c-dc45-4964-a7e8-6152e90b15be</t>
+          <t>9aa927aa-cb34-45bc-92e7-26bfcb22ae4c</t>
         </is>
       </c>
       <c r="C113" t="b">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1e7330dc-bb0a-444c-967f-088a5338b891</t>
+          <t>f4dd2b27-40b9-4024-ad58-af3dbf6befdf</t>
         </is>
       </c>
       <c r="C114" t="b">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>41b38a67-1f64-4ecc-a6ab-6e582ddff90f</t>
+          <t>8a5af868-c12d-4cba-b1b8-e40e12904faf</t>
         </is>
       </c>
       <c r="C115" t="b">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>c80e226c-e7aa-4c80-a79e-ebe0ed500fbe</t>
+          <t>2d004edf-399c-4fbd-8582-8cfd81acacbf</t>
         </is>
       </c>
       <c r="C116" t="b">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7833e174-abc5-49b4-be76-b2e3be854d7b</t>
+          <t>46e9bcd9-0de3-41da-a8c5-01509c0c0487</t>
         </is>
       </c>
       <c r="C117" t="b">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>60b9643b-0881-49d1-ac41-c033fda5c483</t>
+          <t>76f34cd0-e89e-43df-b949-23b206ace7fd</t>
         </is>
       </c>
       <c r="C118" t="b">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>61fe1e3d-8de8-4637-bd7a-023a3bc04a56</t>
+          <t>ace42842-28e0-4447-9be9-043baa73d86f</t>
         </is>
       </c>
       <c r="C119" t="b">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4daab51d-06a3-4f0d-9aa0-eb4cfa19681f</t>
+          <t>be27f6c8-2c6d-4d9e-948a-e57857a0f547</t>
         </is>
       </c>
       <c r="C120" t="b">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3b1fe548-1449-4d56-9830-30e42cd3962f</t>
+          <t>184e02f2-0f5a-495e-81cd-880a42a6b609</t>
         </is>
       </c>
       <c r="C121" t="b">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2e269c7a-bc77-4068-a8c6-09caa1e70b3e</t>
+          <t>5348db8d-77c0-4d9d-819d-ccd61738ff91</t>
         </is>
       </c>
       <c r="C122" t="b">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>922ea59a-282b-45f8-87c6-25c231d19b8c</t>
+          <t>74c46482-bce7-4624-b428-58bb6a007373</t>
         </is>
       </c>
       <c r="C123" t="b">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>c80e226c-e7aa-4c80-a79e-ebe0ed500fbe</t>
+          <t>2d004edf-399c-4fbd-8582-8cfd81acacbf</t>
         </is>
       </c>
       <c r="C124" t="b">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7833e174-abc5-49b4-be76-b2e3be854d7b</t>
+          <t>46e9bcd9-0de3-41da-a8c5-01509c0c0487</t>
         </is>
       </c>
       <c r="C125" t="b">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>60b9643b-0881-49d1-ac41-c033fda5c483</t>
+          <t>76f34cd0-e89e-43df-b949-23b206ace7fd</t>
         </is>
       </c>
       <c r="C126" t="b">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>61fe1e3d-8de8-4637-bd7a-023a3bc04a56</t>
+          <t>ace42842-28e0-4447-9be9-043baa73d86f</t>
         </is>
       </c>
       <c r="C127" t="b">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4daab51d-06a3-4f0d-9aa0-eb4cfa19681f</t>
+          <t>be27f6c8-2c6d-4d9e-948a-e57857a0f547</t>
         </is>
       </c>
       <c r="C128" t="b">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3b1fe548-1449-4d56-9830-30e42cd3962f</t>
+          <t>184e02f2-0f5a-495e-81cd-880a42a6b609</t>
         </is>
       </c>
       <c r="C129" t="b">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2e269c7a-bc77-4068-a8c6-09caa1e70b3e</t>
+          <t>5348db8d-77c0-4d9d-819d-ccd61738ff91</t>
         </is>
       </c>
       <c r="C130" t="b">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>922ea59a-282b-45f8-87c6-25c231d19b8c</t>
+          <t>74c46482-bce7-4624-b428-58bb6a007373</t>
         </is>
       </c>
       <c r="C131" t="b">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>c80e226c-e7aa-4c80-a79e-ebe0ed500fbe</t>
+          <t>2d004edf-399c-4fbd-8582-8cfd81acacbf</t>
         </is>
       </c>
       <c r="C132" t="b">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7833e174-abc5-49b4-be76-b2e3be854d7b</t>
+          <t>46e9bcd9-0de3-41da-a8c5-01509c0c0487</t>
         </is>
       </c>
       <c r="C133" t="b">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>60b9643b-0881-49d1-ac41-c033fda5c483</t>
+          <t>76f34cd0-e89e-43df-b949-23b206ace7fd</t>
         </is>
       </c>
       <c r="C134" t="b">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>61fe1e3d-8de8-4637-bd7a-023a3bc04a56</t>
+          <t>ace42842-28e0-4447-9be9-043baa73d86f</t>
         </is>
       </c>
       <c r="C135" t="b">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>4daab51d-06a3-4f0d-9aa0-eb4cfa19681f</t>
+          <t>be27f6c8-2c6d-4d9e-948a-e57857a0f547</t>
         </is>
       </c>
       <c r="C136" t="b">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3b1fe548-1449-4d56-9830-30e42cd3962f</t>
+          <t>184e02f2-0f5a-495e-81cd-880a42a6b609</t>
         </is>
       </c>
       <c r="C137" t="b">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2e269c7a-bc77-4068-a8c6-09caa1e70b3e</t>
+          <t>5348db8d-77c0-4d9d-819d-ccd61738ff91</t>
         </is>
       </c>
       <c r="C138" t="b">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>922ea59a-282b-45f8-87c6-25c231d19b8c</t>
+          <t>74c46482-bce7-4624-b428-58bb6a007373</t>
         </is>
       </c>
       <c r="C139" t="b">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>c80e226c-e7aa-4c80-a79e-ebe0ed500fbe</t>
+          <t>2d004edf-399c-4fbd-8582-8cfd81acacbf</t>
         </is>
       </c>
       <c r="C140" t="b">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7833e174-abc5-49b4-be76-b2e3be854d7b</t>
+          <t>46e9bcd9-0de3-41da-a8c5-01509c0c0487</t>
         </is>
       </c>
       <c r="C141" t="b">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>60b9643b-0881-49d1-ac41-c033fda5c483</t>
+          <t>76f34cd0-e89e-43df-b949-23b206ace7fd</t>
         </is>
       </c>
       <c r="C142" t="b">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>61fe1e3d-8de8-4637-bd7a-023a3bc04a56</t>
+          <t>ace42842-28e0-4447-9be9-043baa73d86f</t>
         </is>
       </c>
       <c r="C143" t="b">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>4daab51d-06a3-4f0d-9aa0-eb4cfa19681f</t>
+          <t>be27f6c8-2c6d-4d9e-948a-e57857a0f547</t>
         </is>
       </c>
       <c r="C144" t="b">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3b1fe548-1449-4d56-9830-30e42cd3962f</t>
+          <t>184e02f2-0f5a-495e-81cd-880a42a6b609</t>
         </is>
       </c>
       <c r="C145" t="b">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2e269c7a-bc77-4068-a8c6-09caa1e70b3e</t>
+          <t>5348db8d-77c0-4d9d-819d-ccd61738ff91</t>
         </is>
       </c>
       <c r="C146" t="b">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>922ea59a-282b-45f8-87c6-25c231d19b8c</t>
+          <t>74c46482-bce7-4624-b428-58bb6a007373</t>
         </is>
       </c>
       <c r="C147" t="b">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>c80e226c-e7aa-4c80-a79e-ebe0ed500fbe</t>
+          <t>2d004edf-399c-4fbd-8582-8cfd81acacbf</t>
         </is>
       </c>
       <c r="C148" t="b">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7833e174-abc5-49b4-be76-b2e3be854d7b</t>
+          <t>46e9bcd9-0de3-41da-a8c5-01509c0c0487</t>
         </is>
       </c>
       <c r="C149" t="b">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>60b9643b-0881-49d1-ac41-c033fda5c483</t>
+          <t>76f34cd0-e89e-43df-b949-23b206ace7fd</t>
         </is>
       </c>
       <c r="C150" t="b">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>61fe1e3d-8de8-4637-bd7a-023a3bc04a56</t>
+          <t>ace42842-28e0-4447-9be9-043baa73d86f</t>
         </is>
       </c>
       <c r="C151" t="b">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4daab51d-06a3-4f0d-9aa0-eb4cfa19681f</t>
+          <t>be27f6c8-2c6d-4d9e-948a-e57857a0f547</t>
         </is>
       </c>
       <c r="C152" t="b">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3b1fe548-1449-4d56-9830-30e42cd3962f</t>
+          <t>184e02f2-0f5a-495e-81cd-880a42a6b609</t>
         </is>
       </c>
       <c r="C153" t="b">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2e269c7a-bc77-4068-a8c6-09caa1e70b3e</t>
+          <t>5348db8d-77c0-4d9d-819d-ccd61738ff91</t>
         </is>
       </c>
       <c r="C154" t="b">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>922ea59a-282b-45f8-87c6-25c231d19b8c</t>
+          <t>74c46482-bce7-4624-b428-58bb6a007373</t>
         </is>
       </c>
       <c r="C155" t="b">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>c80e226c-e7aa-4c80-a79e-ebe0ed500fbe</t>
+          <t>2d004edf-399c-4fbd-8582-8cfd81acacbf</t>
         </is>
       </c>
       <c r="C156" t="b">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7833e174-abc5-49b4-be76-b2e3be854d7b</t>
+          <t>46e9bcd9-0de3-41da-a8c5-01509c0c0487</t>
         </is>
       </c>
       <c r="C157" t="b">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>60b9643b-0881-49d1-ac41-c033fda5c483</t>
+          <t>76f34cd0-e89e-43df-b949-23b206ace7fd</t>
         </is>
       </c>
       <c r="C158" t="b">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>61fe1e3d-8de8-4637-bd7a-023a3bc04a56</t>
+          <t>ace42842-28e0-4447-9be9-043baa73d86f</t>
         </is>
       </c>
       <c r="C159" t="b">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4daab51d-06a3-4f0d-9aa0-eb4cfa19681f</t>
+          <t>be27f6c8-2c6d-4d9e-948a-e57857a0f547</t>
         </is>
       </c>
       <c r="C160" t="b">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>3b1fe548-1449-4d56-9830-30e42cd3962f</t>
+          <t>184e02f2-0f5a-495e-81cd-880a42a6b609</t>
         </is>
       </c>
       <c r="C161" t="b">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2e269c7a-bc77-4068-a8c6-09caa1e70b3e</t>
+          <t>5348db8d-77c0-4d9d-819d-ccd61738ff91</t>
         </is>
       </c>
       <c r="C162" t="b">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>922ea59a-282b-45f8-87c6-25c231d19b8c</t>
+          <t>74c46482-bce7-4624-b428-58bb6a007373</t>
         </is>
       </c>
       <c r="C163" t="b">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>67719a3c-97b5-419a-93d1-ac67d2790ea8</t>
+          <t>9ac8b8c7-9059-4f90-9eee-12b427f45b35</t>
         </is>
       </c>
       <c r="C164" t="b">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>b4a1d8d5-8755-4f0c-be0d-31f66fd24dd5</t>
+          <t>6081bf84-191d-442a-87ec-7fde1cead1f5</t>
         </is>
       </c>
       <c r="C165" t="b">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>b7791b79-930d-464d-9166-7097ffd6c45e</t>
+          <t>6baae17d-3770-4861-b4f1-ed5a1470b88e</t>
         </is>
       </c>
       <c r="C166" t="b">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>78ad8a66-6674-4926-8c4e-ad4249d6a229</t>
+          <t>20ea0e39-7505-4245-881d-c736b3ced2b9</t>
         </is>
       </c>
       <c r="C167" t="b">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>30142cdf-fcc1-45d0-92da-93b8221253c2</t>
+          <t>a691f620-f8fc-4657-806d-f0a40e669523</t>
         </is>
       </c>
       <c r="C168" t="b">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>db5d1efd-0263-43fb-9037-59d0abb93ef0</t>
+          <t>7c08996c-42a3-4903-9616-e29043f859bb</t>
         </is>
       </c>
       <c r="C169" t="b">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>57c00b85-dcec-4183-b966-5be4960d354b</t>
+          <t>8d3f77ee-4bdb-4b8c-8ebc-80cb0b9a17fa</t>
         </is>
       </c>
       <c r="C170" t="b">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>67719a3c-97b5-419a-93d1-ac67d2790ea8</t>
+          <t>9ac8b8c7-9059-4f90-9eee-12b427f45b35</t>
         </is>
       </c>
       <c r="C171" t="b">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>b4a1d8d5-8755-4f0c-be0d-31f66fd24dd5</t>
+          <t>6081bf84-191d-442a-87ec-7fde1cead1f5</t>
         </is>
       </c>
       <c r="C172" t="b">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>b7791b79-930d-464d-9166-7097ffd6c45e</t>
+          <t>6baae17d-3770-4861-b4f1-ed5a1470b88e</t>
         </is>
       </c>
       <c r="C173" t="b">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>78ad8a66-6674-4926-8c4e-ad4249d6a229</t>
+          <t>20ea0e39-7505-4245-881d-c736b3ced2b9</t>
         </is>
       </c>
       <c r="C174" t="b">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>30142cdf-fcc1-45d0-92da-93b8221253c2</t>
+          <t>a691f620-f8fc-4657-806d-f0a40e669523</t>
         </is>
       </c>
       <c r="C175" t="b">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>db5d1efd-0263-43fb-9037-59d0abb93ef0</t>
+          <t>7c08996c-42a3-4903-9616-e29043f859bb</t>
         </is>
       </c>
       <c r="C176" t="b">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>57c00b85-dcec-4183-b966-5be4960d354b</t>
+          <t>8d3f77ee-4bdb-4b8c-8ebc-80cb0b9a17fa</t>
         </is>
       </c>
       <c r="C177" t="b">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>67719a3c-97b5-419a-93d1-ac67d2790ea8</t>
+          <t>9ac8b8c7-9059-4f90-9eee-12b427f45b35</t>
         </is>
       </c>
       <c r="C178" t="b">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>b4a1d8d5-8755-4f0c-be0d-31f66fd24dd5</t>
+          <t>6081bf84-191d-442a-87ec-7fde1cead1f5</t>
         </is>
       </c>
       <c r="C179" t="b">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>b7791b79-930d-464d-9166-7097ffd6c45e</t>
+          <t>6baae17d-3770-4861-b4f1-ed5a1470b88e</t>
         </is>
       </c>
       <c r="C180" t="b">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>78ad8a66-6674-4926-8c4e-ad4249d6a229</t>
+          <t>20ea0e39-7505-4245-881d-c736b3ced2b9</t>
         </is>
       </c>
       <c r="C181" t="b">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>30142cdf-fcc1-45d0-92da-93b8221253c2</t>
+          <t>a691f620-f8fc-4657-806d-f0a40e669523</t>
         </is>
       </c>
       <c r="C182" t="b">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>db5d1efd-0263-43fb-9037-59d0abb93ef0</t>
+          <t>7c08996c-42a3-4903-9616-e29043f859bb</t>
         </is>
       </c>
       <c r="C183" t="b">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>57c00b85-dcec-4183-b966-5be4960d354b</t>
+          <t>8d3f77ee-4bdb-4b8c-8ebc-80cb0b9a17fa</t>
         </is>
       </c>
       <c r="C184" t="b">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>67719a3c-97b5-419a-93d1-ac67d2790ea8</t>
+          <t>9ac8b8c7-9059-4f90-9eee-12b427f45b35</t>
         </is>
       </c>
       <c r="C185" t="b">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>b4a1d8d5-8755-4f0c-be0d-31f66fd24dd5</t>
+          <t>6081bf84-191d-442a-87ec-7fde1cead1f5</t>
         </is>
       </c>
       <c r="C186" t="b">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>b7791b79-930d-464d-9166-7097ffd6c45e</t>
+          <t>6baae17d-3770-4861-b4f1-ed5a1470b88e</t>
         </is>
       </c>
       <c r="C187" t="b">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>78ad8a66-6674-4926-8c4e-ad4249d6a229</t>
+          <t>20ea0e39-7505-4245-881d-c736b3ced2b9</t>
         </is>
       </c>
       <c r="C188" t="b">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>30142cdf-fcc1-45d0-92da-93b8221253c2</t>
+          <t>a691f620-f8fc-4657-806d-f0a40e669523</t>
         </is>
       </c>
       <c r="C189" t="b">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>db5d1efd-0263-43fb-9037-59d0abb93ef0</t>
+          <t>7c08996c-42a3-4903-9616-e29043f859bb</t>
         </is>
       </c>
       <c r="C190" t="b">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>57c00b85-dcec-4183-b966-5be4960d354b</t>
+          <t>8d3f77ee-4bdb-4b8c-8ebc-80cb0b9a17fa</t>
         </is>
       </c>
       <c r="C191" t="b">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>67719a3c-97b5-419a-93d1-ac67d2790ea8</t>
+          <t>9ac8b8c7-9059-4f90-9eee-12b427f45b35</t>
         </is>
       </c>
       <c r="C192" t="b">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>b4a1d8d5-8755-4f0c-be0d-31f66fd24dd5</t>
+          <t>6081bf84-191d-442a-87ec-7fde1cead1f5</t>
         </is>
       </c>
       <c r="C193" t="b">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>b7791b79-930d-464d-9166-7097ffd6c45e</t>
+          <t>6baae17d-3770-4861-b4f1-ed5a1470b88e</t>
         </is>
       </c>
       <c r="C194" t="b">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>78ad8a66-6674-4926-8c4e-ad4249d6a229</t>
+          <t>20ea0e39-7505-4245-881d-c736b3ced2b9</t>
         </is>
       </c>
       <c r="C195" t="b">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>30142cdf-fcc1-45d0-92da-93b8221253c2</t>
+          <t>a691f620-f8fc-4657-806d-f0a40e669523</t>
         </is>
       </c>
       <c r="C196" t="b">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>db5d1efd-0263-43fb-9037-59d0abb93ef0</t>
+          <t>7c08996c-42a3-4903-9616-e29043f859bb</t>
         </is>
       </c>
       <c r="C197" t="b">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>57c00b85-dcec-4183-b966-5be4960d354b</t>
+          <t>8d3f77ee-4bdb-4b8c-8ebc-80cb0b9a17fa</t>
         </is>
       </c>
       <c r="C198" t="b">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>67719a3c-97b5-419a-93d1-ac67d2790ea8</t>
+          <t>9ac8b8c7-9059-4f90-9eee-12b427f45b35</t>
         </is>
       </c>
       <c r="C199" t="b">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>b4a1d8d5-8755-4f0c-be0d-31f66fd24dd5</t>
+          <t>6081bf84-191d-442a-87ec-7fde1cead1f5</t>
         </is>
       </c>
       <c r="C200" t="b">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>b7791b79-930d-464d-9166-7097ffd6c45e</t>
+          <t>6baae17d-3770-4861-b4f1-ed5a1470b88e</t>
         </is>
       </c>
       <c r="C201" t="b">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>78ad8a66-6674-4926-8c4e-ad4249d6a229</t>
+          <t>20ea0e39-7505-4245-881d-c736b3ced2b9</t>
         </is>
       </c>
       <c r="C202" t="b">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>30142cdf-fcc1-45d0-92da-93b8221253c2</t>
+          <t>a691f620-f8fc-4657-806d-f0a40e669523</t>
         </is>
       </c>
       <c r="C203" t="b">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>db5d1efd-0263-43fb-9037-59d0abb93ef0</t>
+          <t>7c08996c-42a3-4903-9616-e29043f859bb</t>
         </is>
       </c>
       <c r="C204" t="b">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>57c00b85-dcec-4183-b966-5be4960d354b</t>
+          <t>8d3f77ee-4bdb-4b8c-8ebc-80cb0b9a17fa</t>
         </is>
       </c>
       <c r="C205" t="b">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>67719a3c-97b5-419a-93d1-ac67d2790ea8</t>
+          <t>9ac8b8c7-9059-4f90-9eee-12b427f45b35</t>
         </is>
       </c>
       <c r="C206" t="b">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>b4a1d8d5-8755-4f0c-be0d-31f66fd24dd5</t>
+          <t>6081bf84-191d-442a-87ec-7fde1cead1f5</t>
         </is>
       </c>
       <c r="C207" t="b">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>b7791b79-930d-464d-9166-7097ffd6c45e</t>
+          <t>6baae17d-3770-4861-b4f1-ed5a1470b88e</t>
         </is>
       </c>
       <c r="C208" t="b">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>78ad8a66-6674-4926-8c4e-ad4249d6a229</t>
+          <t>20ea0e39-7505-4245-881d-c736b3ced2b9</t>
         </is>
       </c>
       <c r="C209" t="b">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>30142cdf-fcc1-45d0-92da-93b8221253c2</t>
+          <t>a691f620-f8fc-4657-806d-f0a40e669523</t>
         </is>
       </c>
       <c r="C210" t="b">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>db5d1efd-0263-43fb-9037-59d0abb93ef0</t>
+          <t>7c08996c-42a3-4903-9616-e29043f859bb</t>
         </is>
       </c>
       <c r="C211" t="b">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>57c00b85-dcec-4183-b966-5be4960d354b</t>
+          <t>8d3f77ee-4bdb-4b8c-8ebc-80cb0b9a17fa</t>
         </is>
       </c>
       <c r="C212" t="b">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>67719a3c-97b5-419a-93d1-ac67d2790ea8</t>
+          <t>9ac8b8c7-9059-4f90-9eee-12b427f45b35</t>
         </is>
       </c>
       <c r="C213" t="b">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>b4a1d8d5-8755-4f0c-be0d-31f66fd24dd5</t>
+          <t>6081bf84-191d-442a-87ec-7fde1cead1f5</t>
         </is>
       </c>
       <c r="C214" t="b">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>b7791b79-930d-464d-9166-7097ffd6c45e</t>
+          <t>6baae17d-3770-4861-b4f1-ed5a1470b88e</t>
         </is>
       </c>
       <c r="C215" t="b">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>78ad8a66-6674-4926-8c4e-ad4249d6a229</t>
+          <t>20ea0e39-7505-4245-881d-c736b3ced2b9</t>
         </is>
       </c>
       <c r="C216" t="b">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>30142cdf-fcc1-45d0-92da-93b8221253c2</t>
+          <t>a691f620-f8fc-4657-806d-f0a40e669523</t>
         </is>
       </c>
       <c r="C217" t="b">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>db5d1efd-0263-43fb-9037-59d0abb93ef0</t>
+          <t>7c08996c-42a3-4903-9616-e29043f859bb</t>
         </is>
       </c>
       <c r="C218" t="b">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>57c00b85-dcec-4183-b966-5be4960d354b</t>
+          <t>8d3f77ee-4bdb-4b8c-8ebc-80cb0b9a17fa</t>
         </is>
       </c>
       <c r="C219" t="b">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>67719a3c-97b5-419a-93d1-ac67d2790ea8</t>
+          <t>9ac8b8c7-9059-4f90-9eee-12b427f45b35</t>
         </is>
       </c>
       <c r="C220" t="b">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>b4a1d8d5-8755-4f0c-be0d-31f66fd24dd5</t>
+          <t>6081bf84-191d-442a-87ec-7fde1cead1f5</t>
         </is>
       </c>
       <c r="C221" t="b">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>b7791b79-930d-464d-9166-7097ffd6c45e</t>
+          <t>6baae17d-3770-4861-b4f1-ed5a1470b88e</t>
         </is>
       </c>
       <c r="C222" t="b">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>78ad8a66-6674-4926-8c4e-ad4249d6a229</t>
+          <t>20ea0e39-7505-4245-881d-c736b3ced2b9</t>
         </is>
       </c>
       <c r="C223" t="b">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>30142cdf-fcc1-45d0-92da-93b8221253c2</t>
+          <t>a691f620-f8fc-4657-806d-f0a40e669523</t>
         </is>
       </c>
       <c r="C224" t="b">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>db5d1efd-0263-43fb-9037-59d0abb93ef0</t>
+          <t>7c08996c-42a3-4903-9616-e29043f859bb</t>
         </is>
       </c>
       <c r="C225" t="b">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>57c00b85-dcec-4183-b966-5be4960d354b</t>
+          <t>8d3f77ee-4bdb-4b8c-8ebc-80cb0b9a17fa</t>
         </is>
       </c>
       <c r="C226" t="b">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>67719a3c-97b5-419a-93d1-ac67d2790ea8</t>
+          <t>9ac8b8c7-9059-4f90-9eee-12b427f45b35</t>
         </is>
       </c>
       <c r="C227" t="b">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>b4a1d8d5-8755-4f0c-be0d-31f66fd24dd5</t>
+          <t>6081bf84-191d-442a-87ec-7fde1cead1f5</t>
         </is>
       </c>
       <c r="C228" t="b">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>b7791b79-930d-464d-9166-7097ffd6c45e</t>
+          <t>6baae17d-3770-4861-b4f1-ed5a1470b88e</t>
         </is>
       </c>
       <c r="C229" t="b">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>78ad8a66-6674-4926-8c4e-ad4249d6a229</t>
+          <t>20ea0e39-7505-4245-881d-c736b3ced2b9</t>
         </is>
       </c>
       <c r="C230" t="b">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>30142cdf-fcc1-45d0-92da-93b8221253c2</t>
+          <t>a691f620-f8fc-4657-806d-f0a40e669523</t>
         </is>
       </c>
       <c r="C231" t="b">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>db5d1efd-0263-43fb-9037-59d0abb93ef0</t>
+          <t>7c08996c-42a3-4903-9616-e29043f859bb</t>
         </is>
       </c>
       <c r="C232" t="b">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>57c00b85-dcec-4183-b966-5be4960d354b</t>
+          <t>8d3f77ee-4bdb-4b8c-8ebc-80cb0b9a17fa</t>
         </is>
       </c>
       <c r="C233" t="b">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>8894872e-c260-4607-86bc-ef3ac32354ab</t>
+          <t>ada0d8e1-7143-4db4-a835-f33f8bd0d93e</t>
         </is>
       </c>
       <c r="C234" t="b">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>29820b40-02d7-4a16-bbac-94c94d207517</t>
+          <t>77ef5ee1-2752-4cad-8a84-94fe6e69de2d</t>
         </is>
       </c>
       <c r="C235" t="b">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>099eef3b-9c13-4399-948b-e7270b2743d7</t>
+          <t>888c29c4-2c39-45d0-b508-825412755dae</t>
         </is>
       </c>
       <c r="C236" t="b">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>8894872e-c260-4607-86bc-ef3ac32354ab</t>
+          <t>ada0d8e1-7143-4db4-a835-f33f8bd0d93e</t>
         </is>
       </c>
       <c r="C237" t="b">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>29820b40-02d7-4a16-bbac-94c94d207517</t>
+          <t>77ef5ee1-2752-4cad-8a84-94fe6e69de2d</t>
         </is>
       </c>
       <c r="C238" t="b">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>099eef3b-9c13-4399-948b-e7270b2743d7</t>
+          <t>888c29c4-2c39-45d0-b508-825412755dae</t>
         </is>
       </c>
       <c r="C239" t="b">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>8894872e-c260-4607-86bc-ef3ac32354ab</t>
+          <t>ada0d8e1-7143-4db4-a835-f33f8bd0d93e</t>
         </is>
       </c>
       <c r="C240" t="b">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>29820b40-02d7-4a16-bbac-94c94d207517</t>
+          <t>77ef5ee1-2752-4cad-8a84-94fe6e69de2d</t>
         </is>
       </c>
       <c r="C241" t="b">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>099eef3b-9c13-4399-948b-e7270b2743d7</t>
+          <t>888c29c4-2c39-45d0-b508-825412755dae</t>
         </is>
       </c>
       <c r="C242" t="b">
